--- a/product_selector_out/STM32G4x1 - diff.xlsx
+++ b/product_selector_out/STM32G4x1 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -541,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2170</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="18">
@@ -1477,18 +1483,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1500,13 +1510,13 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -1518,18 +1528,18 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -1546,25 +1556,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1587,7 +1601,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1610,7 +1624,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1633,7 +1647,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1656,7 +1670,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1679,7 +1693,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1702,41 +1716,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -1748,18 +1766,18 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1771,18 +1789,18 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -1794,18 +1812,18 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -1817,18 +1835,18 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -1840,18 +1858,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1863,18 +1881,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -1886,18 +1904,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -1909,18 +1927,18 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -1932,18 +1950,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -1955,18 +1973,18 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -1978,18 +1996,18 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2001,18 +2019,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2024,18 +2042,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2047,18 +2065,18 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -2070,18 +2088,18 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2093,18 +2111,18 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2116,18 +2134,18 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2139,30 +2157,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2185,7 +2207,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2208,41 +2230,45 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -2251,8 +2277,123 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E88"/>
+  <autoFilter ref="A18:E93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32G4x1 - diff.xlsx
+++ b/product_selector_out/STM32G4x1 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2240</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2165</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="18">
@@ -742,18 +742,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431VB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -770,13 +770,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -788,18 +788,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -816,13 +816,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -834,18 +834,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -857,18 +857,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -972,18 +972,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -995,18 +995,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1018,18 +1018,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1110,18 +1110,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1133,18 +1133,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1156,18 +1156,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1179,18 +1179,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1202,18 +1202,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1225,18 +1225,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1248,18 +1248,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1271,18 +1271,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1340,18 +1340,18 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1363,18 +1363,18 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -1386,18 +1386,18 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1409,18 +1409,18 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1478,34 +1478,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1528,7 +1524,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,34 +1547,30 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1601,7 +1593,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1624,7 +1616,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1647,7 +1639,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1670,18 +1662,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -1693,18 +1685,18 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -1716,68 +1708,68 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1789,18 +1781,18 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -1812,18 +1804,18 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -1835,41 +1827,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1881,18 +1877,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -1904,18 +1900,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -1927,7 +1923,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1950,7 +1946,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1973,7 +1969,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1996,7 +1992,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2019,18 +2015,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2042,30 +2038,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2111,18 +2111,18 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2134,18 +2134,18 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2157,34 +2157,30 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2207,7 +2203,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2230,34 +2226,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2280,7 +2272,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2303,7 +2295,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2326,7 +2318,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2349,18 +2341,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -2372,18 +2364,18 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2392,8 +2384,591 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32G431M8</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32G431M8</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32G431C8</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32G431C8</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32G431C8</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32G431MB</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32G431MB</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32G431MB</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32G431C6</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32G431C6</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32G431C6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E93"/>
+  <autoFilter ref="A18:E118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>